--- a/output/pdf_financials_xlsx/TRAN.xlsx
+++ b/output/pdf_financials_xlsx/TRAN.xlsx
@@ -1078,7 +1078,7 @@
         <v>-0.735445</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.377076</v>
+        <v>-1.846656</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-10.125768</v>
@@ -1298,7 +1298,7 @@
         <v>-0.735445</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.111866</v>
+        <v>-1.111866</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-9.788779999999999</v>
@@ -1427,7 +1427,7 @@
         <v>-0.735445</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.111866</v>
+        <v>-1.111866</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-9.788779999999999</v>
@@ -1603,7 +1603,7 @@
         <v>-0.735445</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.377076</v>
+        <v>-1.846656</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-10.125768</v>
@@ -1689,7 +1689,7 @@
         <v>-0.7320489999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.377076</v>
+        <v>-1.846656</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-10.125768</v>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>27.83275956752033</v>
+        <v>-136.3054992943566</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-608.1334152524508</v>
@@ -1789,7 +1789,7 @@
         <v>-100</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>194.8652261082646</v>
+        <v>-39.79030203784571</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-3.328024106418397</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>82.06912943093847</v>
+        <v>-82.06912943093847</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-587.8945885936638</v>
@@ -4419,40 +4419,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>8.772368999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>9.519562000000001</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>9.972595999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>10.233688</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.449403</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>10.501365</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>10.548296</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.666052</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.686123</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>10.468816</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.494419</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>10.600449</v>
       </c>
     </row>
     <row r="93">
@@ -4705,7 +4705,7 @@
         <v>-0.735445</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>1.111866</v>
+        <v>-1.111866</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-9.788779999999999</v>
@@ -5501,22 +5501,22 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.111504</v>
+        <v>-0.648738</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.471649</v>
+        <v>0.085378</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>3.528004</v>
+        <v>0.295297</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>7.681991</v>
+        <v>6.919068</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-0.0512</v>
+        <v>-0.747315</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-0.045</v>
+        <v>-0.528892</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>-2.04452</v>
@@ -7358,7 +7358,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9248,7 +9252,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -10772,7 +10780,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -12280,7 +12292,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -13610,7 +13626,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -14580,7 +14600,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -15400,7 +15424,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E122" s="5" t="n">
         <v>8.772368999999999</v>
       </c>
@@ -17609,7 +17637,7 @@
         <v>-0.735445</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>1.111866</v>
+        <v>-1.111866</v>
       </c>
       <c r="M151" s="5" t="n">
         <v>-9.788779999999999</v>
@@ -24078,7 +24106,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -26794,7 +26826,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E275" s="5" t="n">
         <v>-0.760242</v>
       </c>
@@ -35361,7 +35397,7 @@
         </is>
       </c>
       <c r="L390" s="5" t="n">
-        <v>1.111866</v>
+        <v>-1.111866</v>
       </c>
       <c r="M390" s="5" t="n">
         <v>-9.788779999999999</v>

--- a/output/pdf_financials_xlsx/TRAN.xlsx
+++ b/output/pdf_financials_xlsx/TRAN.xlsx
@@ -885,22 +885,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001341</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003875</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006428</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.007282</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004389</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001159</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -915,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.020153</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003515</v>
       </c>
     </row>
     <row r="13">
@@ -1582,22 +1582,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.565698</v>
+        <v>-0.567039</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.825546</v>
+        <v>-0.829421</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.485124</v>
+        <v>-4.491552</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.361864000000001</v>
+        <v>-8.369146000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.830058</v>
+        <v>-0.834447</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.513476</v>
+        <v>-0.514635</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.735445</v>
@@ -1612,10 +1612,10 @@
         <v>-0.711582</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.921728</v>
+        <v>-1.941881</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.667273</v>
+        <v>-1.670788</v>
       </c>
     </row>
     <row r="28">
@@ -1668,22 +1668,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.517035</v>
+        <v>-0.5183759999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.799143</v>
+        <v>-0.803018</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.473041</v>
+        <v>-4.479469</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.356540000000001</v>
+        <v>-8.363822000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.828877</v>
+        <v>-0.833266</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.513476</v>
+        <v>-0.514635</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.7320489999999999</v>
@@ -1698,10 +1698,10 @@
         <v>-0.711582</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.921728</v>
+        <v>-1.941881</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.667273</v>
+        <v>-1.670788</v>
       </c>
     </row>
     <row r="30">
@@ -1755,10 +1755,10 @@
         <v>-52.79072355389375</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-385.4325197055697</v>
+        <v>-389.4745181411581</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-1317.117351976933</v>
+        <v>-1319.894142275941</v>
       </c>
     </row>
     <row r="31">
@@ -1875,40 +1875,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.089992</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.52693</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.883259</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.755881</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.647415</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07420300000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.042094</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.128401</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.030123</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003593</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.7810240000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.858135</v>
       </c>
     </row>
     <row r="35">
@@ -1961,40 +1961,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.089992</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.52693</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.883259</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.755881</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.001751</v>
+        <v>0.649166</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.005909</v>
+        <v>0.080112</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.003362</v>
+        <v>0.045456</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.005222</v>
+        <v>0.133623</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.006454</v>
+        <v>0.036577</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003593</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.70438</v>
+        <v>2.485404</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.28044</v>
+        <v>1.138575</v>
       </c>
     </row>
     <row r="37">
@@ -2477,40 +2477,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.184949</v>
+        <v>0.094957</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.562301</v>
+        <v>0.035371</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.918256</v>
+        <v>0.034997</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.027207</v>
+        <v>0.271326</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.676905</v>
+        <v>0.02949</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.079716</v>
+        <v>0.005513</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.123259</v>
+        <v>0.081165</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.158803</v>
+        <v>0.030402</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.036927</v>
+        <v>0.006804</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.004921</v>
+        <v>0.001328</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.824061</v>
+        <v>0.043037</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.993906</v>
+        <v>0.135771</v>
       </c>
     </row>
     <row r="49">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -39240,7 +39240,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -42392,7 +42392,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E483" s="5" t="n">

--- a/output/pdf_financials_xlsx/TRAN.xlsx
+++ b/output/pdf_financials_xlsx/TRAN.xlsx
@@ -5175,19 +5175,19 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.089911</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.244877</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.273297</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.225907</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.284632</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002054</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006578</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
         <v>-0.003592</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03051</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -5384,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.121013</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -5399,13 +5399,13 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.000924</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>2.664008</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.954458</v>
       </c>
     </row>
     <row r="116">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002054</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006578</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         <v>-0.003592</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03051</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.035863</v>
+        <v>-0.037917</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.990167</v>
+        <v>-0.996745</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.63056</v>
@@ -6286,7 +6286,7 @@
         <v>1.164086</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.16665</v>
+        <v>-1.19716</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-1.293322</v>
@@ -17954,7 +17954,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -18680,7 +18684,11 @@
           <t>Proceeds from sale of marketable securities 6</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -18982,7 +18990,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -21508,7 +21520,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E204" s="5" t="n">
         <v>-0.001719</v>
       </c>
@@ -23512,7 +23528,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -24852,7 +24872,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -27058,7 +27082,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="n">
         <v>-0.002054</v>
       </c>
@@ -33336,7 +33364,11 @@
           <t>Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -35282,7 +35314,11 @@
           <t>Deferred Income Tax Recovery 20</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -36870,7 +36906,11 @@
           <t>Deferred Income Tax Recovery 24</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -38178,7 +38218,11 @@
           <t>Deferred Income Tax Recovery 21</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -39540,7 +39584,11 @@
           <t>Deferred Income Tax Recovery 14</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -40818,7 +40866,11 @@
           <t>Deferred Income Tax Recovery 12</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -42916,7 +42968,11 @@
           <t>Deferred Income Tax Recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E490" s="5" t="n">
         <v>0.001719</v>
       </c>
